--- a/src/时序数据预测-系列/单元时序预测-水质参数/Tb/data/样点1.xlsx
+++ b/src/时序数据预测-系列/单元时序预测-水质参数/Tb/data/样点1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xxqhh\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xxqhh\Desktop\Tb-云量50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6167E777-09BF-4F64-B8CA-594BCDF8439B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3B0E0E6-0E25-47D7-89F8-60BE90444C23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,9 +64,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="0.00000000000"/>
+    <numFmt numFmtId="176" formatCode="0.00000000000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -103,6 +103,12 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -126,11 +132,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -140,6 +146,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -442,7 +451,7 @@
       <c r="A2">
         <v>201511</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="5">
         <v>84.010911682200003</v>
       </c>
       <c r="C2">
@@ -462,7 +471,7 @@
       <c r="A3">
         <v>201512</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="5">
         <v>68.278514573799995</v>
       </c>
       <c r="C3">
@@ -482,7 +491,7 @@
       <c r="A4">
         <v>201601</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="5">
         <v>42.249370736300001</v>
       </c>
       <c r="C4">
@@ -502,7 +511,7 @@
       <c r="A5">
         <v>201602</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="5">
         <v>86.294664697100004</v>
       </c>
       <c r="C5">
@@ -522,7 +531,7 @@
       <c r="A6">
         <v>201603</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="5">
         <v>48.8242529901</v>
       </c>
       <c r="C6">
@@ -559,7 +568,7 @@
       <c r="A8">
         <v>201605</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="5">
         <v>250.85945372699999</v>
       </c>
       <c r="C8">
@@ -579,7 +588,7 @@
       <c r="A9">
         <v>201606</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>5</v>
       </c>
       <c r="C9">
@@ -599,7 +608,7 @@
       <c r="A10">
         <v>201607</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="5">
         <v>65.713810851399998</v>
       </c>
       <c r="C10">
@@ -619,7 +628,7 @@
       <c r="A11">
         <v>201608</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="5">
         <v>63.344497904100002</v>
       </c>
       <c r="C11">
@@ -639,7 +648,7 @@
       <c r="A12">
         <v>201609</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="5">
         <v>65.853839199800007</v>
       </c>
       <c r="C12">
@@ -676,7 +685,7 @@
       <c r="A14">
         <v>201611</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="5">
         <v>23.2779640296</v>
       </c>
       <c r="C14">
@@ -696,7 +705,7 @@
       <c r="A15">
         <v>201612</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="5">
         <v>27.443869837000001</v>
       </c>
       <c r="C15">
@@ -716,7 +725,7 @@
       <c r="A16">
         <v>201701</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="5" t="s">
         <v>5</v>
       </c>
       <c r="C16">
@@ -736,7 +745,7 @@
       <c r="A17">
         <v>201702</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="5">
         <v>63.5856699701</v>
       </c>
       <c r="C17">
@@ -773,7 +782,7 @@
       <c r="A19">
         <v>201704</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19" s="5">
         <v>75.864354454500003</v>
       </c>
       <c r="C19">
@@ -793,7 +802,7 @@
       <c r="A20">
         <v>201705</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" s="5">
         <v>70.583943189300001</v>
       </c>
       <c r="C20">
@@ -813,7 +822,7 @@
       <c r="A21">
         <v>201706</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="5" t="s">
         <v>5</v>
       </c>
       <c r="C21">
@@ -833,7 +842,7 @@
       <c r="A22">
         <v>201707</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B22" s="5">
         <v>85.034901195700002</v>
       </c>
       <c r="C22">
@@ -853,7 +862,7 @@
       <c r="A23">
         <v>201708</v>
       </c>
-      <c r="B23" s="4">
+      <c r="B23" s="5">
         <v>58.001990351700002</v>
       </c>
       <c r="C23">
@@ -873,7 +882,7 @@
       <c r="A24">
         <v>201709</v>
       </c>
-      <c r="B24" s="4">
+      <c r="B24" s="5">
         <v>51.6326022501</v>
       </c>
       <c r="C24">
@@ -893,7 +902,7 @@
       <c r="A25">
         <v>201710</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25" s="5">
         <v>43.581637049599998</v>
       </c>
       <c r="C25">
@@ -913,7 +922,7 @@
       <c r="A26">
         <v>201711</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B26" s="5">
         <v>60.842621580500001</v>
       </c>
       <c r="C26">
@@ -933,7 +942,7 @@
       <c r="A27">
         <v>201712</v>
       </c>
-      <c r="B27" s="4">
+      <c r="B27" s="5">
         <v>45.860688769299998</v>
       </c>
       <c r="C27">
@@ -953,7 +962,7 @@
       <c r="A28">
         <v>201801</v>
       </c>
-      <c r="B28" s="4">
+      <c r="B28" s="5">
         <v>67.193651177500001</v>
       </c>
       <c r="C28">
@@ -973,7 +982,7 @@
       <c r="A29">
         <v>201802</v>
       </c>
-      <c r="B29" s="4">
+      <c r="B29" s="5">
         <v>50.885400300199997</v>
       </c>
       <c r="C29">
@@ -993,7 +1002,7 @@
       <c r="A30">
         <v>201803</v>
       </c>
-      <c r="B30" s="4">
+      <c r="B30" s="5">
         <v>36.167755440500002</v>
       </c>
       <c r="C30">
@@ -1013,7 +1022,7 @@
       <c r="A31">
         <v>201804</v>
       </c>
-      <c r="B31" s="4">
+      <c r="B31" s="5">
         <v>81.306060948099997</v>
       </c>
       <c r="C31">
@@ -1033,7 +1042,7 @@
       <c r="A32">
         <v>201805</v>
       </c>
-      <c r="B32" s="4">
+      <c r="B32" s="5">
         <v>56.368597146500001</v>
       </c>
       <c r="C32">
@@ -1053,7 +1062,7 @@
       <c r="A33">
         <v>201806</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="5" t="s">
         <v>5</v>
       </c>
       <c r="C33">
@@ -1073,7 +1082,7 @@
       <c r="A34">
         <v>201807</v>
       </c>
-      <c r="B34" s="4">
+      <c r="B34" s="5">
         <v>57.2938894451</v>
       </c>
       <c r="C34">
@@ -1093,7 +1102,7 @@
       <c r="A35">
         <v>201808</v>
       </c>
-      <c r="B35" s="4">
+      <c r="B35" s="5">
         <v>69.114803373000001</v>
       </c>
       <c r="C35">
@@ -1113,7 +1122,7 @@
       <c r="A36">
         <v>201809</v>
       </c>
-      <c r="B36" s="4">
+      <c r="B36" s="5">
         <v>56.999160783299999</v>
       </c>
       <c r="C36">
@@ -1133,7 +1142,7 @@
       <c r="A37">
         <v>201810</v>
       </c>
-      <c r="B37" s="4">
+      <c r="B37" s="5">
         <v>62.572465650799998</v>
       </c>
       <c r="C37">
@@ -1153,7 +1162,7 @@
       <c r="A38">
         <v>201811</v>
       </c>
-      <c r="B38" s="4">
+      <c r="B38" s="5">
         <v>46.610272911300001</v>
       </c>
       <c r="C38">
@@ -1173,7 +1182,7 @@
       <c r="A39">
         <v>201812</v>
       </c>
-      <c r="B39" s="4">
+      <c r="B39" s="5">
         <v>46.013235053800003</v>
       </c>
       <c r="C39">
@@ -1193,7 +1202,7 @@
       <c r="A40">
         <v>201901</v>
       </c>
-      <c r="B40" s="4">
+      <c r="B40" s="5">
         <v>40.638620996500002</v>
       </c>
       <c r="C40">
@@ -1213,7 +1222,7 @@
       <c r="A41">
         <v>201902</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="5" t="s">
         <v>5</v>
       </c>
       <c r="C41">
@@ -1233,7 +1242,7 @@
       <c r="A42">
         <v>201903</v>
       </c>
-      <c r="B42" s="4">
+      <c r="B42" s="5">
         <v>77.103561165299993</v>
       </c>
       <c r="C42">
@@ -1253,7 +1262,7 @@
       <c r="A43">
         <v>201904</v>
       </c>
-      <c r="B43" s="4">
+      <c r="B43" s="5">
         <v>80.877253304999996</v>
       </c>
       <c r="C43">
@@ -1273,7 +1282,7 @@
       <c r="A44">
         <v>201905</v>
       </c>
-      <c r="B44" s="4">
+      <c r="B44" s="5">
         <v>102.36377109599999</v>
       </c>
       <c r="C44">
@@ -1293,7 +1302,7 @@
       <c r="A45">
         <v>201906</v>
       </c>
-      <c r="B45" s="4">
+      <c r="B45" s="5">
         <v>82.647097187400007</v>
       </c>
       <c r="C45">
@@ -1313,7 +1322,7 @@
       <c r="A46">
         <v>201907</v>
       </c>
-      <c r="B46" s="4">
+      <c r="B46" s="5">
         <v>62.312878291799997</v>
       </c>
       <c r="C46">
@@ -1333,7 +1342,7 @@
       <c r="A47">
         <v>201908</v>
       </c>
-      <c r="B47" s="4">
+      <c r="B47" s="5">
         <v>84.240046799799998</v>
       </c>
       <c r="C47">
@@ -1353,7 +1362,7 @@
       <c r="A48">
         <v>201909</v>
       </c>
-      <c r="B48" s="4">
+      <c r="B48" s="5">
         <v>71.809224870899996</v>
       </c>
       <c r="C48">
@@ -1373,7 +1382,7 @@
       <c r="A49">
         <v>201910</v>
       </c>
-      <c r="B49" s="4">
+      <c r="B49" s="5">
         <v>54.328670871600004</v>
       </c>
       <c r="C49">
@@ -1393,7 +1402,7 @@
       <c r="A50">
         <v>201911</v>
       </c>
-      <c r="B50" s="4">
+      <c r="B50" s="5">
         <v>49.987355420199997</v>
       </c>
       <c r="C50">
@@ -1413,7 +1422,7 @@
       <c r="A51">
         <v>201912</v>
       </c>
-      <c r="B51" s="4">
+      <c r="B51" s="5">
         <v>47.219163017600003</v>
       </c>
       <c r="C51">
@@ -1433,7 +1442,7 @@
       <c r="A52">
         <v>202001</v>
       </c>
-      <c r="B52" s="4">
+      <c r="B52" s="5">
         <v>73.308054639100007</v>
       </c>
       <c r="C52">
@@ -1453,7 +1462,7 @@
       <c r="A53">
         <v>202002</v>
       </c>
-      <c r="B53" s="4">
+      <c r="B53" s="5">
         <v>84.778785624099996</v>
       </c>
       <c r="C53">
@@ -1473,7 +1482,7 @@
       <c r="A54">
         <v>202003</v>
       </c>
-      <c r="B54" s="4">
+      <c r="B54" s="5">
         <v>65.124567560900005</v>
       </c>
       <c r="C54">
@@ -1493,7 +1502,7 @@
       <c r="A55">
         <v>202004</v>
       </c>
-      <c r="B55" s="4">
+      <c r="B55" s="5">
         <v>77.931122376299996</v>
       </c>
       <c r="C55">
@@ -1513,7 +1522,7 @@
       <c r="A56">
         <v>202005</v>
       </c>
-      <c r="B56" s="4">
+      <c r="B56" s="5">
         <v>76.636287788800004</v>
       </c>
       <c r="C56">
@@ -1533,7 +1542,7 @@
       <c r="A57">
         <v>202006</v>
       </c>
-      <c r="B57" s="4">
+      <c r="B57" s="5">
         <v>57.468378161799997</v>
       </c>
       <c r="C57">
@@ -1553,7 +1562,7 @@
       <c r="A58">
         <v>202007</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B58" s="5" t="s">
         <v>5</v>
       </c>
       <c r="C58">
@@ -1573,7 +1582,7 @@
       <c r="A59">
         <v>202008</v>
       </c>
-      <c r="B59" s="4">
+      <c r="B59" s="5">
         <v>47.832445446000001</v>
       </c>
       <c r="C59">
@@ -1593,7 +1602,7 @@
       <c r="A60">
         <v>202009</v>
       </c>
-      <c r="B60" s="4">
+      <c r="B60" s="5">
         <v>72.777795424900006</v>
       </c>
       <c r="C60">
@@ -1613,7 +1622,7 @@
       <c r="A61">
         <v>202010</v>
       </c>
-      <c r="B61" s="4">
+      <c r="B61" s="5">
         <v>46.357171223999998</v>
       </c>
       <c r="C61">
@@ -1633,7 +1642,7 @@
       <c r="A62">
         <v>202011</v>
       </c>
-      <c r="B62" s="4">
+      <c r="B62" s="5">
         <v>36.327112098000001</v>
       </c>
       <c r="C62">
@@ -1653,7 +1662,7 @@
       <c r="A63">
         <v>202012</v>
       </c>
-      <c r="B63" s="4">
+      <c r="B63" s="5">
         <v>37.831113547900003</v>
       </c>
       <c r="C63">
@@ -1673,7 +1682,7 @@
       <c r="A64">
         <v>202101</v>
       </c>
-      <c r="B64" s="4">
+      <c r="B64" s="5">
         <v>49.428238032099998</v>
       </c>
       <c r="C64">
@@ -1693,7 +1702,7 @@
       <c r="A65">
         <v>202102</v>
       </c>
-      <c r="B65" s="4">
+      <c r="B65" s="5">
         <v>21.788824292400001</v>
       </c>
       <c r="C65">
@@ -1713,7 +1722,7 @@
       <c r="A66">
         <v>202103</v>
       </c>
-      <c r="B66" s="4">
+      <c r="B66" s="5">
         <v>49.516908208399997</v>
       </c>
       <c r="C66">
@@ -1733,7 +1742,7 @@
       <c r="A67">
         <v>202104</v>
       </c>
-      <c r="B67" s="4">
+      <c r="B67" s="5">
         <v>60.4183050233</v>
       </c>
       <c r="C67">
@@ -1753,7 +1762,7 @@
       <c r="A68">
         <v>202105</v>
       </c>
-      <c r="B68" s="4">
+      <c r="B68" s="5">
         <v>99.084107795199998</v>
       </c>
       <c r="C68">
@@ -1773,7 +1782,7 @@
       <c r="A69">
         <v>202106</v>
       </c>
-      <c r="B69" s="4">
+      <c r="B69" s="5">
         <v>85.492240589700003</v>
       </c>
       <c r="C69">
@@ -1793,7 +1802,7 @@
       <c r="A70">
         <v>202107</v>
       </c>
-      <c r="B70" s="4">
+      <c r="B70" s="5">
         <v>43.035694131100001</v>
       </c>
       <c r="C70">
@@ -1813,7 +1822,7 @@
       <c r="A71">
         <v>202108</v>
       </c>
-      <c r="B71" s="4">
+      <c r="B71" s="5">
         <v>44.2861736447</v>
       </c>
       <c r="C71">
@@ -1833,7 +1842,7 @@
       <c r="A72">
         <v>202109</v>
       </c>
-      <c r="B72" s="4">
+      <c r="B72" s="5">
         <v>66.063205128199996</v>
       </c>
       <c r="C72">
@@ -1853,7 +1862,7 @@
       <c r="A73">
         <v>202110</v>
       </c>
-      <c r="B73" s="4">
+      <c r="B73" s="5">
         <v>35.2724561116</v>
       </c>
       <c r="C73">
@@ -1873,7 +1882,7 @@
       <c r="A74">
         <v>202111</v>
       </c>
-      <c r="B74" s="4">
+      <c r="B74" s="5">
         <v>50.124913334200002</v>
       </c>
       <c r="C74">
@@ -1893,7 +1902,7 @@
       <c r="A75">
         <v>202112</v>
       </c>
-      <c r="B75" s="4">
+      <c r="B75" s="5">
         <v>47.543614749900001</v>
       </c>
       <c r="C75">
@@ -1913,7 +1922,7 @@
       <c r="A76">
         <v>202201</v>
       </c>
-      <c r="B76" s="4">
+      <c r="B76" s="5">
         <v>34.886896905500002</v>
       </c>
       <c r="C76">
@@ -1933,7 +1942,7 @@
       <c r="A77">
         <v>202202</v>
       </c>
-      <c r="B77" s="4">
+      <c r="B77" s="5">
         <v>71.398125339800004</v>
       </c>
       <c r="C77">
@@ -1953,7 +1962,7 @@
       <c r="A78">
         <v>202203</v>
       </c>
-      <c r="B78" s="4">
+      <c r="B78" s="5">
         <v>77.672313841800005</v>
       </c>
       <c r="C78">
@@ -1973,7 +1982,7 @@
       <c r="A79">
         <v>202204</v>
       </c>
-      <c r="B79" s="4">
+      <c r="B79" s="5">
         <v>85.706140691800002</v>
       </c>
       <c r="C79">
@@ -1993,7 +2002,7 @@
       <c r="A80">
         <v>202205</v>
       </c>
-      <c r="B80" s="4">
+      <c r="B80" s="5">
         <v>99.4007627692</v>
       </c>
       <c r="C80">
@@ -2013,7 +2022,7 @@
       <c r="A81">
         <v>202206</v>
       </c>
-      <c r="B81" s="4">
+      <c r="B81" s="5">
         <v>99.686897832499994</v>
       </c>
       <c r="C81">
@@ -2033,7 +2042,7 @@
       <c r="A82">
         <v>202207</v>
       </c>
-      <c r="B82" s="4">
+      <c r="B82" s="5">
         <v>93.853400536799995</v>
       </c>
       <c r="C82">
@@ -2053,7 +2062,7 @@
       <c r="A83">
         <v>202208</v>
       </c>
-      <c r="B83" s="4">
+      <c r="B83" s="5">
         <v>92.947705440700005</v>
       </c>
       <c r="C83">
@@ -2073,7 +2082,7 @@
       <c r="A84">
         <v>202209</v>
       </c>
-      <c r="B84" s="4" t="s">
+      <c r="B84" s="5" t="s">
         <v>5</v>
       </c>
       <c r="C84">
@@ -2093,7 +2102,7 @@
       <c r="A85">
         <v>202210</v>
       </c>
-      <c r="B85" s="4">
+      <c r="B85" s="5">
         <v>83.751603233200001</v>
       </c>
       <c r="C85">
@@ -2113,7 +2122,7 @@
       <c r="A86">
         <v>202211</v>
       </c>
-      <c r="B86" s="4">
+      <c r="B86" s="5">
         <v>67.182016039000004</v>
       </c>
       <c r="C86">
@@ -2133,7 +2142,7 @@
       <c r="A87">
         <v>202212</v>
       </c>
-      <c r="B87" s="4">
+      <c r="B87" s="5">
         <v>88.656402107000005</v>
       </c>
       <c r="C87">
@@ -2153,7 +2162,7 @@
       <c r="A88">
         <v>202301</v>
       </c>
-      <c r="B88" s="4">
+      <c r="B88" s="5">
         <v>81.746017404200003</v>
       </c>
       <c r="C88">
@@ -2173,7 +2182,7 @@
       <c r="A89">
         <v>202302</v>
       </c>
-      <c r="B89" s="4">
+      <c r="B89" s="5">
         <v>65.603493910899999</v>
       </c>
       <c r="C89">
@@ -2193,7 +2202,7 @@
       <c r="A90">
         <v>202303</v>
       </c>
-      <c r="B90" s="4">
+      <c r="B90" s="5">
         <v>73.293199960600006</v>
       </c>
       <c r="C90">
@@ -2213,7 +2222,7 @@
       <c r="A91">
         <v>202304</v>
       </c>
-      <c r="B91" s="4">
+      <c r="B91" s="5">
         <v>71.435930591399995</v>
       </c>
       <c r="C91">
@@ -2233,7 +2242,7 @@
       <c r="A92">
         <v>202305</v>
       </c>
-      <c r="B92" s="4">
+      <c r="B92" s="5">
         <v>60.749465857799997</v>
       </c>
       <c r="C92">
@@ -2253,7 +2262,7 @@
       <c r="A93">
         <v>202306</v>
       </c>
-      <c r="B93" s="4" t="s">
+      <c r="B93" s="5" t="s">
         <v>5</v>
       </c>
       <c r="C93">
@@ -2273,8 +2282,8 @@
       <c r="A94">
         <v>202307</v>
       </c>
-      <c r="B94" s="4">
-        <v>95.4695971676</v>
+      <c r="B94" s="5">
+        <v>80.843307428599999</v>
       </c>
       <c r="C94">
         <v>24.901</v>
@@ -2293,8 +2302,8 @@
       <c r="A95">
         <v>202308</v>
       </c>
-      <c r="B95" s="4">
-        <v>81.327099980200003</v>
+      <c r="B95" s="5">
+        <v>50.450959988400001</v>
       </c>
       <c r="C95">
         <v>15.27</v>
@@ -2313,8 +2322,8 @@
       <c r="A96">
         <v>202309</v>
       </c>
-      <c r="B96" s="4">
-        <v>85.851638097800006</v>
+      <c r="B96" s="5">
+        <v>50.974923327900001</v>
       </c>
       <c r="C96">
         <v>13.159000000000001</v>
@@ -2333,8 +2342,8 @@
       <c r="A97">
         <v>202310</v>
       </c>
-      <c r="B97" s="4">
-        <v>80.078985534300003</v>
+      <c r="B97" s="5">
+        <v>30.557139465100001</v>
       </c>
       <c r="C97">
         <v>1.843</v>
@@ -2353,8 +2362,8 @@
       <c r="A98">
         <v>202311</v>
       </c>
-      <c r="B98" s="4">
-        <v>77.878367900900002</v>
+      <c r="B98" s="5">
+        <v>26.591973260100001</v>
       </c>
       <c r="C98">
         <v>3.532</v>
@@ -2370,8 +2379,8 @@
       <c r="A99">
         <v>202312</v>
       </c>
-      <c r="B99" s="4">
-        <v>74.110048568400003</v>
+      <c r="B99" s="5">
+        <v>23.922575369</v>
       </c>
       <c r="C99">
         <v>4.1360000000000001</v>
